--- a/import_requests_sap.xlsx
+++ b/import_requests_sap.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25DAC03-E7ED-4B44-86B5-781A80F238D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8191951-8ADE-4171-8927-231FDD6D7688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="2700" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -442,9 +442,11 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3900000220</v>
-      </c>
-      <c r="B2" s="4"/>
+        <v>3700000173</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2200004948</v>
+      </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>

--- a/import_requests_sap.xlsx
+++ b/import_requests_sap.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8191951-8ADE-4171-8927-231FDD6D7688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EC53F9-C94D-4583-9390-F6A92E696BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="300" yWindow="2700" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,9 +441,6 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>3700000173</v>
-      </c>
       <c r="B2" s="4">
         <v>2200004948</v>
       </c>

--- a/import_requests_sap.xlsx
+++ b/import_requests_sap.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EC53F9-C94D-4583-9390-F6A92E696BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC2585B-9C6C-4144-BD3E-68EBCB2AC502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="300" yWindow="2700" windowWidth="17280" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,9 +441,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="4">
+      <c r="A2">
         <v>2200004948</v>
       </c>
+      <c r="B2" s="4"/>
       <c r="C2" s="2">
         <v>1</v>
       </c>
